--- a/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
   <si>
     <t>Ce ConceptMap présente deux groupes de mapping : 
  - Groupe Mapping 1 : entre le modèle métier de l'auteur et l'élément CDA author
- - Groupe Mapping 2 : entre l'élément CDA author et Composition.author en FHIR</t>
+ - Groupe Mapping 2 : entre l'élément CDA author et l'élément FHIR Composition.author</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -123,55 +123,46 @@
     <t>author</t>
   </si>
   <si>
+    <t>Auteur.roleFonctionnel</t>
+  </si>
+  <si>
+    <t>author.functionCode</t>
+  </si>
+  <si>
+    <t>Auteur.horodatageParticipation</t>
+  </si>
+  <si>
+    <t>author.time</t>
+  </si>
+  <si>
     <t>Auteur.auteurPersonneStructure</t>
   </si>
   <si>
-    <t>author.assignedAuthor.assignedPerson</t>
-  </si>
-  <si>
-    <t>Auteur.auteurPersonneStructure.structure</t>
-  </si>
-  <si>
-    <t>author.assignedAuthor.representedOrganization</t>
+    <t>author.assignedAuthor</t>
   </si>
   <si>
     <t>Auteur.auteurSysteme</t>
   </si>
   <si>
-    <t>author.assignedAuthor.assignedAuthoringDevice</t>
-  </si>
-  <si>
-    <t>Auteur.auteurSysteme.structure</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
   </si>
   <si>
     <t>Composition.author</t>
   </si>
   <si>
-    <t>author.functionCode</t>
+    <t>Composition.author.extension:time</t>
   </si>
   <si>
     <t>Composition.author.PractitionerRole.code</t>
   </si>
   <si>
-    <t>author.time</t>
-  </si>
-  <si>
-    <t>Composition.author.extension:time</t>
-  </si>
-  <si>
-    <t>Composition.author.PractitionerRole.Practitioner</t>
-  </si>
-  <si>
-    <t>Composition.author.PractitionerRole.Organization</t>
+    <t>Composition.author.PractitionerRole</t>
+  </si>
+  <si>
+    <t>Composition.author.Patient</t>
   </si>
   <si>
     <t>Composition.author.Device</t>
-  </si>
-  <si>
-    <t>Composition.author.Device.owner</t>
   </si>
 </sst>
 </file>
@@ -525,7 +516,7 @@
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -536,7 +527,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -588,53 +579,53 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -647,22 +638,9 @@
         <v>33</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E9" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingAuteurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
